--- a/شركة مناجم الفوسفات الاردنية م.م.xlsx
+++ b/شركة مناجم الفوسفات الاردنية م.م.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF63913C-00CB-46FC-B548-F5674817AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559E380B-8F9D-415F-B123-DDDDD8300D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB6FE7FE-32E2-42EC-9A3F-95BA7E45AF41}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="137">
   <si>
     <t>الرقم</t>
   </si>
@@ -429,6 +429,24 @@
   </si>
   <si>
     <t>المتبقي</t>
+  </si>
+  <si>
+    <t>5099*34882*36090</t>
+  </si>
+  <si>
+    <t>5092*3768*19078</t>
+  </si>
+  <si>
+    <t>عبدالله اشرف الفرجات</t>
+  </si>
+  <si>
+    <t>يزن اشرف الفرجات</t>
+  </si>
+  <si>
+    <t>تبارك اشرف النصرات</t>
+  </si>
+  <si>
+    <t>مليحه خالد الفرجات</t>
   </si>
 </sst>
 </file>
@@ -487,9 +505,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -497,30 +518,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="9"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="17"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -684,6 +681,30 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="9"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="17"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -698,21 +719,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7CCDE891-F8F7-43DD-A1DB-B2098D8A823B}" name="Table1" displayName="Table1" ref="A1:L265" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:L265" xr:uid="{7CCDE891-F8F7-43DD-A1DB-B2098D8A823B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7CCDE891-F8F7-43DD-A1DB-B2098D8A823B}" name="Table1" displayName="Table1" ref="A1:L270" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:L270" xr:uid="{7CCDE891-F8F7-43DD-A1DB-B2098D8A823B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L265">
     <sortCondition ref="F1:F265"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8DAD9B10-750A-43FE-B8AA-B4EE0F27CB73}" name="الرقم" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{4D0EF1C0-3C2C-48AD-8CAE-375A8F3FF62D}" name="رقم الموظف /رقم البطاقة" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7E24F566-0689-479E-AF73-B0ACBD117394}" name="اسم المريض" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{F15DE86A-C987-4132-AFC8-AFEAEBA07F14}" name="رقم النموذج" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{6530B592-1615-4925-AA64-9869C4597C18}" name="نوع المستفيد" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{D2168DCF-127B-4737-A96B-F0B152B2355D}" name="تاريخ البيع" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A7E836F5-9B1A-424F-A5DB-FB26A73FF25D}" name="قيمة الفاتورة" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{939191EA-4949-4B70-89B6-39792ACC5232}" name="قيمة المشاركة" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{A4B8458B-46FA-4143-BDF8-C6E8A5A9EBC6}" name="صافي القيمة" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8DAD9B10-750A-43FE-B8AA-B4EE0F27CB73}" name="الرقم" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{4D0EF1C0-3C2C-48AD-8CAE-375A8F3FF62D}" name="رقم الموظف /رقم البطاقة" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{7E24F566-0689-479E-AF73-B0ACBD117394}" name="اسم المريض" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{F15DE86A-C987-4132-AFC8-AFEAEBA07F14}" name="رقم النموذج" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6530B592-1615-4925-AA64-9869C4597C18}" name="نوع المستفيد" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{D2168DCF-127B-4737-A96B-F0B152B2355D}" name="تاريخ البيع" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{A7E836F5-9B1A-424F-A5DB-FB26A73FF25D}" name="قيمة الفاتورة" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{939191EA-4949-4B70-89B6-39792ACC5232}" name="قيمة المشاركة" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{A4B8458B-46FA-4143-BDF8-C6E8A5A9EBC6}" name="صافي القيمة" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{23D45D88-432C-4239-86C3-6857A65F3A79}" name="القيمة المطلوبة">
       <calculatedColumnFormula>G2*0.94-H2</calculatedColumnFormula>
     </tableColumn>
@@ -1042,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98254183-715B-438E-8B50-7B0250B84D9E}">
-  <dimension ref="A1:L265"/>
+  <dimension ref="A1:L270"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -1126,11 +1147,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J2">
-        <f>G2*0.94-H2</f>
+        <f t="shared" ref="J2:J65" si="0">G2*0.94-H2</f>
         <v>149.99059999999997</v>
       </c>
       <c r="L2">
-        <f>J2-K2</f>
+        <f t="shared" ref="L2:L65" si="1">J2-K2</f>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -1163,11 +1184,11 @@
         <v>85.823999999999998</v>
       </c>
       <c r="J3">
-        <f>G3*0.94-H3</f>
+        <f t="shared" si="0"/>
         <v>79.387199999999993</v>
       </c>
       <c r="L3">
-        <f>J3-K3</f>
+        <f t="shared" si="1"/>
         <v>79.387199999999993</v>
       </c>
     </row>
@@ -1200,11 +1221,11 @@
         <v>60.671999999999997</v>
       </c>
       <c r="J4">
-        <f>G4*0.94-H4</f>
+        <f t="shared" si="0"/>
         <v>56.121599999999994</v>
       </c>
       <c r="L4">
-        <f>J4-K4</f>
+        <f t="shared" si="1"/>
         <v>56.121599999999994</v>
       </c>
     </row>
@@ -1237,11 +1258,11 @@
         <v>40.607999999999997</v>
       </c>
       <c r="J5">
-        <f>G5*0.94-H5</f>
+        <f t="shared" si="0"/>
         <v>37.562399999999997</v>
       </c>
       <c r="L5">
-        <f>J5-K5</f>
+        <f t="shared" si="1"/>
         <v>37.562399999999997</v>
       </c>
     </row>
@@ -1274,11 +1295,11 @@
         <v>54.12</v>
       </c>
       <c r="J6">
-        <f>G6*0.94-H6</f>
+        <f t="shared" si="0"/>
         <v>50.061</v>
       </c>
       <c r="L6">
-        <f>J6-K6</f>
+        <f t="shared" si="1"/>
         <v>50.061</v>
       </c>
     </row>
@@ -1311,11 +1332,11 @@
         <v>120.22199999999999</v>
       </c>
       <c r="J7">
-        <f>G7*0.94-H7</f>
+        <f t="shared" si="0"/>
         <v>111.20531999999999</v>
       </c>
       <c r="L7">
-        <f>J7-K7</f>
+        <f t="shared" si="1"/>
         <v>111.20531999999999</v>
       </c>
     </row>
@@ -1348,11 +1369,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J8">
-        <f>G8*0.94-H8</f>
+        <f t="shared" si="0"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L8">
-        <f>J8-K8</f>
+        <f t="shared" si="1"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -1385,11 +1406,11 @@
         <v>15.352</v>
       </c>
       <c r="J9">
-        <f>G9*0.94-H9</f>
+        <f t="shared" si="0"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L9">
-        <f>J9-K9</f>
+        <f t="shared" si="1"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -1422,11 +1443,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J10">
-        <f>G10*0.94-H10</f>
+        <f t="shared" si="0"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L10">
-        <f>J10-K10</f>
+        <f t="shared" si="1"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -1459,11 +1480,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J11">
-        <f>G11*0.94-H11</f>
+        <f t="shared" si="0"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L11">
-        <f>J11-K11</f>
+        <f t="shared" si="1"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -1496,11 +1517,11 @@
         <v>115.16</v>
       </c>
       <c r="J12">
-        <f>G12*0.94-H12</f>
+        <f t="shared" si="0"/>
         <v>106.523</v>
       </c>
       <c r="L12">
-        <f>J12-K12</f>
+        <f t="shared" si="1"/>
         <v>106.523</v>
       </c>
     </row>
@@ -1533,11 +1554,11 @@
         <v>27.952000000000002</v>
       </c>
       <c r="J13">
-        <f>G13*0.94-H13</f>
+        <f t="shared" si="0"/>
         <v>25.855599999999995</v>
       </c>
       <c r="L13">
-        <f>J13-K13</f>
+        <f t="shared" si="1"/>
         <v>25.855599999999995</v>
       </c>
     </row>
@@ -1570,11 +1591,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J14">
-        <f>G14*0.94-H14</f>
+        <f t="shared" si="0"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L14">
-        <f>J14-K14</f>
+        <f t="shared" si="1"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -1607,11 +1628,11 @@
         <v>29.6</v>
       </c>
       <c r="J15">
-        <f>G15*0.94-H15</f>
+        <f t="shared" si="0"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L15">
-        <f>J15-K15</f>
+        <f t="shared" si="1"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -1644,11 +1665,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J16">
-        <f>G16*0.94-H16</f>
+        <f t="shared" si="0"/>
         <v>21.2972</v>
       </c>
       <c r="L16">
-        <f>J16-K16</f>
+        <f t="shared" si="1"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -1681,11 +1702,11 @@
         <v>24.928000000000001</v>
       </c>
       <c r="J17">
-        <f>G17*0.94-H17</f>
+        <f t="shared" si="0"/>
         <v>23.058399999999999</v>
       </c>
       <c r="L17">
-        <f>J17-K17</f>
+        <f t="shared" si="1"/>
         <v>23.058399999999999</v>
       </c>
     </row>
@@ -1718,11 +1739,11 @@
         <v>165.274</v>
       </c>
       <c r="J18">
-        <f>G18*0.94-H18</f>
+        <f t="shared" si="0"/>
         <v>152.87848000000002</v>
       </c>
       <c r="L18">
-        <f>J18-K18</f>
+        <f t="shared" si="1"/>
         <v>152.87848000000002</v>
       </c>
     </row>
@@ -1755,11 +1776,11 @@
         <v>7.56</v>
       </c>
       <c r="J19">
-        <f>G19*0.94-H19</f>
+        <f t="shared" si="0"/>
         <v>6.9929999999999994</v>
       </c>
       <c r="L19">
-        <f>J19-K19</f>
+        <f t="shared" si="1"/>
         <v>6.9929999999999994</v>
       </c>
     </row>
@@ -1792,11 +1813,11 @@
         <v>85.695999999999998</v>
       </c>
       <c r="J20">
-        <f>G20*0.94-H20</f>
+        <f t="shared" si="0"/>
         <v>79.268799999999999</v>
       </c>
       <c r="L20">
-        <f>J20-K20</f>
+        <f t="shared" si="1"/>
         <v>79.268799999999999</v>
       </c>
     </row>
@@ -1829,11 +1850,11 @@
         <v>60.671999999999997</v>
       </c>
       <c r="J21">
-        <f>G21*0.94-H21</f>
+        <f t="shared" si="0"/>
         <v>56.121599999999994</v>
       </c>
       <c r="L21">
-        <f>J21-K21</f>
+        <f t="shared" si="1"/>
         <v>56.121599999999994</v>
       </c>
     </row>
@@ -1866,11 +1887,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J22">
-        <f>G22*0.94-H22</f>
+        <f t="shared" si="0"/>
         <v>149.99059999999997</v>
       </c>
       <c r="L22">
-        <f>J22-K22</f>
+        <f t="shared" si="1"/>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -1903,11 +1924,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J23">
-        <f>G23*0.94-H23</f>
+        <f t="shared" si="0"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L23">
-        <f>J23-K23</f>
+        <f t="shared" si="1"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -1940,11 +1961,11 @@
         <v>40.607999999999997</v>
       </c>
       <c r="J24">
-        <f>G24*0.94-H24</f>
+        <f t="shared" si="0"/>
         <v>37.562399999999997</v>
       </c>
       <c r="L24">
-        <f>J24-K24</f>
+        <f t="shared" si="1"/>
         <v>37.562399999999997</v>
       </c>
     </row>
@@ -1977,11 +1998,11 @@
         <v>51.735999999999997</v>
       </c>
       <c r="J25">
-        <f>G25*0.94-H25</f>
+        <f t="shared" si="0"/>
         <v>47.855800000000002</v>
       </c>
       <c r="L25">
-        <f>J25-K25</f>
+        <f t="shared" si="1"/>
         <v>47.855800000000002</v>
       </c>
     </row>
@@ -2014,11 +2035,11 @@
         <v>94.793999999999997</v>
       </c>
       <c r="J26">
-        <f>G26*0.94-H26</f>
+        <f t="shared" si="0"/>
         <v>87.684480000000008</v>
       </c>
       <c r="L26">
-        <f>J26-K26</f>
+        <f t="shared" si="1"/>
         <v>87.684480000000008</v>
       </c>
     </row>
@@ -2051,11 +2072,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J27">
-        <f>G27*0.94-H27</f>
+        <f t="shared" si="0"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L27">
-        <f>J27-K27</f>
+        <f t="shared" si="1"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -2088,11 +2109,11 @@
         <v>20.143999999999998</v>
       </c>
       <c r="J28">
-        <f>G28*0.94-H28</f>
+        <f t="shared" si="0"/>
         <v>18.633200000000002</v>
       </c>
       <c r="L28">
-        <f>J28-K28</f>
+        <f t="shared" si="1"/>
         <v>18.633200000000002</v>
       </c>
     </row>
@@ -2125,11 +2146,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J29">
-        <f>G29*0.94-H29</f>
+        <f t="shared" si="0"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L29">
-        <f>J29-K29</f>
+        <f t="shared" si="1"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -2162,11 +2183,11 @@
         <v>91.176000000000002</v>
       </c>
       <c r="J30">
-        <f>G30*0.94-H30</f>
+        <f t="shared" si="0"/>
         <v>84.337800000000001</v>
       </c>
       <c r="L30">
-        <f>J30-K30</f>
+        <f t="shared" si="1"/>
         <v>84.337800000000001</v>
       </c>
     </row>
@@ -2199,11 +2220,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J31">
-        <f>G31*0.94-H31</f>
+        <f t="shared" si="0"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L31">
-        <f>J31-K31</f>
+        <f t="shared" si="1"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -2236,11 +2257,11 @@
         <v>29.6</v>
       </c>
       <c r="J32">
-        <f>G32*0.94-H32</f>
+        <f t="shared" si="0"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L32">
-        <f>J32-K32</f>
+        <f t="shared" si="1"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -2273,11 +2294,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J33">
-        <f>G33*0.94-H33</f>
+        <f t="shared" si="0"/>
         <v>21.2972</v>
       </c>
       <c r="L33">
-        <f>J33-K33</f>
+        <f t="shared" si="1"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -2310,11 +2331,11 @@
         <v>158.477</v>
       </c>
       <c r="J34">
-        <f>G34*0.94-H34</f>
+        <f t="shared" si="0"/>
         <v>146.59124</v>
       </c>
       <c r="L34">
-        <f>J34-K34</f>
+        <f t="shared" si="1"/>
         <v>146.59124</v>
       </c>
     </row>
@@ -2347,11 +2368,11 @@
         <v>2.3679999999999999</v>
       </c>
       <c r="J35">
-        <f>G35*0.94-H35</f>
+        <f t="shared" si="0"/>
         <v>2.1903999999999999</v>
       </c>
       <c r="L35">
-        <f>J35-K35</f>
+        <f t="shared" si="1"/>
         <v>2.1903999999999999</v>
       </c>
     </row>
@@ -2384,11 +2405,11 @@
         <v>42.783999999999999</v>
       </c>
       <c r="J36">
-        <f>G36*0.94-H36</f>
+        <f t="shared" si="0"/>
         <v>39.575199999999995</v>
       </c>
       <c r="L36">
-        <f>J36-K36</f>
+        <f t="shared" si="1"/>
         <v>39.575199999999995</v>
       </c>
     </row>
@@ -2421,11 +2442,11 @@
         <v>37.488</v>
       </c>
       <c r="J37">
-        <f>G37*0.94-H37</f>
+        <f t="shared" si="0"/>
         <v>34.676399999999994</v>
       </c>
       <c r="L37">
-        <f>J37-K37</f>
+        <f t="shared" si="1"/>
         <v>34.676399999999994</v>
       </c>
     </row>
@@ -2458,11 +2479,11 @@
         <v>23.288</v>
       </c>
       <c r="J38">
-        <f>G38*0.94-H38</f>
+        <f t="shared" si="0"/>
         <v>21.541399999999999</v>
       </c>
       <c r="L38">
-        <f>J38-K38</f>
+        <f t="shared" si="1"/>
         <v>21.541399999999999</v>
       </c>
     </row>
@@ -2495,11 +2516,11 @@
         <v>42.944000000000003</v>
       </c>
       <c r="J39">
-        <f>G39*0.94-H39</f>
+        <f t="shared" si="0"/>
         <v>39.723199999999991</v>
       </c>
       <c r="L39">
-        <f>J39-K39</f>
+        <f t="shared" si="1"/>
         <v>39.723199999999991</v>
       </c>
     </row>
@@ -2532,11 +2553,11 @@
         <v>39.936</v>
       </c>
       <c r="J40">
-        <f>G40*0.94-H40</f>
+        <f t="shared" si="0"/>
         <v>36.940799999999996</v>
       </c>
       <c r="L40">
-        <f>J40-K40</f>
+        <f t="shared" si="1"/>
         <v>36.940799999999996</v>
       </c>
     </row>
@@ -2569,11 +2590,11 @@
         <v>40.744</v>
       </c>
       <c r="J41">
-        <f>G41*0.94-H41</f>
+        <f t="shared" si="0"/>
         <v>37.688199999999995</v>
       </c>
       <c r="L41">
-        <f>J41-K41</f>
+        <f t="shared" si="1"/>
         <v>37.688199999999995</v>
       </c>
     </row>
@@ -2606,11 +2627,11 @@
         <v>11.528</v>
       </c>
       <c r="J42">
-        <f>G42*0.94-H42</f>
+        <f t="shared" si="0"/>
         <v>10.663399999999999</v>
       </c>
       <c r="L42">
-        <f>J42-K42</f>
+        <f t="shared" si="1"/>
         <v>10.663399999999999</v>
       </c>
     </row>
@@ -2643,11 +2664,11 @@
         <v>91.176000000000002</v>
       </c>
       <c r="J43">
-        <f>G43*0.94-H43</f>
+        <f t="shared" si="0"/>
         <v>84.337800000000001</v>
       </c>
       <c r="L43">
-        <f>J43-K43</f>
+        <f t="shared" si="1"/>
         <v>84.337800000000001</v>
       </c>
     </row>
@@ -2680,11 +2701,11 @@
         <v>113.53</v>
       </c>
       <c r="J44">
-        <f>G44*0.94-H44</f>
+        <f t="shared" si="0"/>
         <v>105.01527999999999</v>
       </c>
       <c r="L44">
-        <f>J44-K44</f>
+        <f t="shared" si="1"/>
         <v>105.01527999999999</v>
       </c>
     </row>
@@ -2717,11 +2738,11 @@
         <v>60.671999999999997</v>
       </c>
       <c r="J45">
-        <f>G45*0.94-H45</f>
+        <f t="shared" si="0"/>
         <v>56.121599999999994</v>
       </c>
       <c r="L45">
-        <f>J45-K45</f>
+        <f t="shared" si="1"/>
         <v>56.121599999999994</v>
       </c>
     </row>
@@ -2754,11 +2775,11 @@
         <v>49.375999999999998</v>
       </c>
       <c r="J46">
-        <f>G46*0.94-H46</f>
+        <f t="shared" si="0"/>
         <v>45.672799999999995</v>
       </c>
       <c r="L46">
-        <f>J46-K46</f>
+        <f t="shared" si="1"/>
         <v>45.672799999999995</v>
       </c>
     </row>
@@ -2791,11 +2812,11 @@
         <v>51.735999999999997</v>
       </c>
       <c r="J47">
-        <f>G47*0.94-H47</f>
+        <f t="shared" si="0"/>
         <v>47.855800000000002</v>
       </c>
       <c r="L47">
-        <f>J47-K47</f>
+        <f t="shared" si="1"/>
         <v>47.855800000000002</v>
       </c>
     </row>
@@ -2828,11 +2849,11 @@
         <v>100.77</v>
       </c>
       <c r="J48">
-        <f>G48*0.94-H48</f>
+        <f t="shared" si="0"/>
         <v>93.212279999999993</v>
       </c>
       <c r="L48">
-        <f>J48-K48</f>
+        <f t="shared" si="1"/>
         <v>93.212279999999993</v>
       </c>
     </row>
@@ -2865,11 +2886,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J49">
-        <f>G49*0.94-H49</f>
+        <f t="shared" si="0"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L49">
-        <f>J49-K49</f>
+        <f t="shared" si="1"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -2902,11 +2923,11 @@
         <v>15.352</v>
       </c>
       <c r="J50">
-        <f>G50*0.94-H50</f>
+        <f t="shared" si="0"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L50">
-        <f>J50-K50</f>
+        <f t="shared" si="1"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -2939,11 +2960,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J51">
-        <f>G51*0.94-H51</f>
+        <f t="shared" si="0"/>
         <v>149.99059999999997</v>
       </c>
       <c r="L51">
-        <f>J51-K51</f>
+        <f t="shared" si="1"/>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -2976,11 +2997,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J52">
-        <f>G52*0.94-H52</f>
+        <f t="shared" si="0"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L52">
-        <f>J52-K52</f>
+        <f t="shared" si="1"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -3013,11 +3034,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J53">
-        <f>G53*0.94-H53</f>
+        <f t="shared" si="0"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L53">
-        <f>J53-K53</f>
+        <f t="shared" si="1"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -3050,11 +3071,11 @@
         <v>43.335999999999999</v>
       </c>
       <c r="J54">
-        <f>G54*0.94-H54</f>
+        <f t="shared" si="0"/>
         <v>40.085800000000006</v>
       </c>
       <c r="L54">
-        <f>J54-K54</f>
+        <f t="shared" si="1"/>
         <v>40.085800000000006</v>
       </c>
     </row>
@@ -3087,11 +3108,11 @@
         <v>165.93799999999999</v>
       </c>
       <c r="J55">
-        <f>G55*0.94-H55</f>
+        <f t="shared" si="0"/>
         <v>153.49267999999998</v>
       </c>
       <c r="L55">
-        <f>J55-K55</f>
+        <f t="shared" si="1"/>
         <v>153.49267999999998</v>
       </c>
     </row>
@@ -3124,11 +3145,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J56">
-        <f>G56*0.94-H56</f>
+        <f t="shared" si="0"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L56">
-        <f>J56-K56</f>
+        <f t="shared" si="1"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -3161,11 +3182,11 @@
         <v>29.6</v>
       </c>
       <c r="J57">
-        <f>G57*0.94-H57</f>
+        <f t="shared" si="0"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L57">
-        <f>J57-K57</f>
+        <f t="shared" si="1"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -3198,11 +3219,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J58">
-        <f>G58*0.94-H58</f>
+        <f t="shared" si="0"/>
         <v>21.2972</v>
       </c>
       <c r="L58">
-        <f>J58-K58</f>
+        <f t="shared" si="1"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -3235,11 +3256,11 @@
         <v>11.608000000000001</v>
       </c>
       <c r="J59">
-        <f>G59*0.94-H59</f>
+        <f t="shared" si="0"/>
         <v>10.737399999999997</v>
       </c>
       <c r="L59">
-        <f>J59-K59</f>
+        <f t="shared" si="1"/>
         <v>10.737399999999997</v>
       </c>
     </row>
@@ -3272,11 +3293,11 @@
         <v>21.335999999999999</v>
       </c>
       <c r="J60">
-        <f>G60*0.94-H60</f>
+        <f t="shared" si="0"/>
         <v>19.735800000000001</v>
       </c>
       <c r="L60">
-        <f>J60-K60</f>
+        <f t="shared" si="1"/>
         <v>19.735800000000001</v>
       </c>
     </row>
@@ -3309,11 +3330,11 @@
         <v>41.792000000000002</v>
       </c>
       <c r="J61">
-        <f>G61*0.94-H61</f>
+        <f t="shared" si="0"/>
         <v>38.657600000000002</v>
       </c>
       <c r="L61">
-        <f>J61-K61</f>
+        <f t="shared" si="1"/>
         <v>38.657600000000002</v>
       </c>
     </row>
@@ -3346,11 +3367,11 @@
         <v>42.944000000000003</v>
       </c>
       <c r="J62">
-        <f>G62*0.94-H62</f>
+        <f t="shared" si="0"/>
         <v>39.723199999999991</v>
       </c>
       <c r="L62">
-        <f>J62-K62</f>
+        <f t="shared" si="1"/>
         <v>39.723199999999991</v>
       </c>
     </row>
@@ -3383,11 +3404,11 @@
         <v>73.88</v>
       </c>
       <c r="J63">
-        <f>G63*0.94-H63</f>
+        <f t="shared" si="0"/>
         <v>68.338999999999984</v>
       </c>
       <c r="L63">
-        <f>J63-K63</f>
+        <f t="shared" si="1"/>
         <v>68.338999999999984</v>
       </c>
     </row>
@@ -3420,11 +3441,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J64">
-        <f>G64*0.94-H64</f>
+        <f t="shared" si="0"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L64">
-        <f>J64-K64</f>
+        <f t="shared" si="1"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -3457,11 +3478,11 @@
         <v>91.176000000000002</v>
       </c>
       <c r="J65">
-        <f>G65*0.94-H65</f>
+        <f t="shared" si="0"/>
         <v>84.337800000000001</v>
       </c>
       <c r="L65">
-        <f>J65-K65</f>
+        <f t="shared" si="1"/>
         <v>84.337800000000001</v>
       </c>
     </row>
@@ -3494,11 +3515,11 @@
         <v>60.671999999999997</v>
       </c>
       <c r="J66">
-        <f>G66*0.94-H66</f>
+        <f t="shared" ref="J66:J129" si="2">G66*0.94-H66</f>
         <v>56.121599999999994</v>
       </c>
       <c r="L66">
-        <f>J66-K66</f>
+        <f t="shared" ref="L66:L129" si="3">J66-K66</f>
         <v>56.121599999999994</v>
       </c>
     </row>
@@ -3531,11 +3552,11 @@
         <v>40.607999999999997</v>
       </c>
       <c r="J67">
-        <f>G67*0.94-H67</f>
+        <f t="shared" si="2"/>
         <v>37.562399999999997</v>
       </c>
       <c r="L67">
-        <f>J67-K67</f>
+        <f t="shared" si="3"/>
         <v>37.562399999999997</v>
       </c>
     </row>
@@ -3568,11 +3589,11 @@
         <v>51.735999999999997</v>
       </c>
       <c r="J68">
-        <f>G68*0.94-H68</f>
+        <f t="shared" si="2"/>
         <v>47.855800000000002</v>
       </c>
       <c r="L68">
-        <f>J68-K68</f>
+        <f t="shared" si="3"/>
         <v>47.855800000000002</v>
       </c>
     </row>
@@ -3605,11 +3626,11 @@
         <v>94.793999999999997</v>
       </c>
       <c r="J69">
-        <f>G69*0.94-H69</f>
+        <f t="shared" si="2"/>
         <v>87.684480000000008</v>
       </c>
       <c r="L69">
-        <f>J69-K69</f>
+        <f t="shared" si="3"/>
         <v>87.684480000000008</v>
       </c>
     </row>
@@ -3642,11 +3663,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J70">
-        <f>G70*0.94-H70</f>
+        <f t="shared" si="2"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L70">
-        <f>J70-K70</f>
+        <f t="shared" si="3"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -3679,11 +3700,11 @@
         <v>15.352</v>
       </c>
       <c r="J71">
-        <f>G71*0.94-H71</f>
+        <f t="shared" si="2"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L71">
-        <f>J71-K71</f>
+        <f t="shared" si="3"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -3716,11 +3737,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J72">
-        <f>G72*0.94-H72</f>
+        <f t="shared" si="2"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L72">
-        <f>J72-K72</f>
+        <f t="shared" si="3"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -3753,11 +3774,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J73">
-        <f>G73*0.94-H73</f>
+        <f t="shared" si="2"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L73">
-        <f>J73-K73</f>
+        <f t="shared" si="3"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -3790,11 +3811,11 @@
         <v>111.41</v>
       </c>
       <c r="J74">
-        <f>G74*0.94-H74</f>
+        <f t="shared" si="2"/>
         <v>103.05427999999998</v>
       </c>
       <c r="L74">
-        <f>J74-K74</f>
+        <f t="shared" si="3"/>
         <v>103.05427999999998</v>
       </c>
     </row>
@@ -3827,11 +3848,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J75">
-        <f>G75*0.94-H75</f>
+        <f t="shared" si="2"/>
         <v>149.99059999999997</v>
       </c>
       <c r="L75">
-        <f>J75-K75</f>
+        <f t="shared" si="3"/>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -3864,11 +3885,11 @@
         <v>12.6</v>
       </c>
       <c r="J76">
-        <f>G76*0.94-H76</f>
+        <f t="shared" si="2"/>
         <v>11.654999999999999</v>
       </c>
       <c r="L76">
-        <f>J76-K76</f>
+        <f t="shared" si="3"/>
         <v>11.654999999999999</v>
       </c>
     </row>
@@ -3901,11 +3922,11 @@
         <v>19.655999999999999</v>
       </c>
       <c r="J77">
-        <f>G77*0.94-H77</f>
+        <f t="shared" si="2"/>
         <v>18.181800000000003</v>
       </c>
       <c r="L77">
-        <f>J77-K77</f>
+        <f t="shared" si="3"/>
         <v>18.181800000000003</v>
       </c>
     </row>
@@ -3938,11 +3959,11 @@
         <v>158.477</v>
       </c>
       <c r="J78">
-        <f>G78*0.94-H78</f>
+        <f t="shared" si="2"/>
         <v>146.59124</v>
       </c>
       <c r="L78">
-        <f>J78-K78</f>
+        <f t="shared" si="3"/>
         <v>146.59124</v>
       </c>
     </row>
@@ -3975,11 +3996,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J79">
-        <f>G79*0.94-H79</f>
+        <f t="shared" si="2"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L79">
-        <f>J79-K79</f>
+        <f t="shared" si="3"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -4012,11 +4033,11 @@
         <v>29.6</v>
       </c>
       <c r="J80">
-        <f>G80*0.94-H80</f>
+        <f t="shared" si="2"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L80">
-        <f>J80-K80</f>
+        <f t="shared" si="3"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -4049,11 +4070,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J81">
-        <f>G81*0.94-H81</f>
+        <f t="shared" si="2"/>
         <v>21.2972</v>
       </c>
       <c r="L81">
-        <f>J81-K81</f>
+        <f t="shared" si="3"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -4086,11 +4107,11 @@
         <v>28.04</v>
       </c>
       <c r="J82">
-        <f>G82*0.94-H82</f>
+        <f t="shared" si="2"/>
         <v>25.936999999999998</v>
       </c>
       <c r="L82">
-        <f>J82-K82</f>
+        <f t="shared" si="3"/>
         <v>25.936999999999998</v>
       </c>
     </row>
@@ -4123,11 +4144,11 @@
         <v>27.832000000000001</v>
       </c>
       <c r="J83">
-        <f>G83*0.94-H83</f>
+        <f t="shared" si="2"/>
         <v>25.744599999999998</v>
       </c>
       <c r="L83">
-        <f>J83-K83</f>
+        <f t="shared" si="3"/>
         <v>25.744599999999998</v>
       </c>
     </row>
@@ -4160,11 +4181,11 @@
         <v>91.176000000000002</v>
       </c>
       <c r="J84">
-        <f>G84*0.94-H84</f>
+        <f t="shared" si="2"/>
         <v>84.337800000000001</v>
       </c>
       <c r="L84">
-        <f>J84-K84</f>
+        <f t="shared" si="3"/>
         <v>84.337800000000001</v>
       </c>
     </row>
@@ -4197,11 +4218,11 @@
         <v>116.59399999999999</v>
       </c>
       <c r="J85">
-        <f>G85*0.94-H85</f>
+        <f t="shared" si="2"/>
         <v>107.84948</v>
       </c>
       <c r="L85">
-        <f>J85-K85</f>
+        <f t="shared" si="3"/>
         <v>107.84948</v>
       </c>
     </row>
@@ -4234,11 +4255,11 @@
         <v>60.671999999999997</v>
       </c>
       <c r="J86">
-        <f>G86*0.94-H86</f>
+        <f t="shared" si="2"/>
         <v>56.121599999999994</v>
       </c>
       <c r="L86">
-        <f>J86-K86</f>
+        <f t="shared" si="3"/>
         <v>56.121599999999994</v>
       </c>
     </row>
@@ -4271,11 +4292,11 @@
         <v>62.695999999999998</v>
       </c>
       <c r="J87">
-        <f>G87*0.94-H87</f>
+        <f t="shared" si="2"/>
         <v>57.9938</v>
       </c>
       <c r="L87">
-        <f>J87-K87</f>
+        <f t="shared" si="3"/>
         <v>57.9938</v>
       </c>
     </row>
@@ -4308,11 +4329,11 @@
         <v>53.368000000000002</v>
       </c>
       <c r="J88">
-        <f>G88*0.94-H88</f>
+        <f t="shared" si="2"/>
         <v>49.365399999999994</v>
       </c>
       <c r="L88">
-        <f>J88-K88</f>
+        <f t="shared" si="3"/>
         <v>49.365399999999994</v>
       </c>
     </row>
@@ -4345,11 +4366,11 @@
         <v>94.793999999999997</v>
       </c>
       <c r="J89">
-        <f>G89*0.94-H89</f>
+        <f t="shared" si="2"/>
         <v>87.684480000000008</v>
       </c>
       <c r="L89">
-        <f>J89-K89</f>
+        <f t="shared" si="3"/>
         <v>87.684480000000008</v>
       </c>
     </row>
@@ -4382,11 +4403,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J90">
-        <f>G90*0.94-H90</f>
+        <f t="shared" si="2"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L90">
-        <f>J90-K90</f>
+        <f t="shared" si="3"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -4419,11 +4440,11 @@
         <v>15.352</v>
       </c>
       <c r="J91">
-        <f>G91*0.94-H91</f>
+        <f t="shared" si="2"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L91">
-        <f>J91-K91</f>
+        <f t="shared" si="3"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -4456,11 +4477,11 @@
         <v>170.048</v>
       </c>
       <c r="J92">
-        <f>G92*0.94-H92</f>
+        <f t="shared" si="2"/>
         <v>157.2944</v>
       </c>
       <c r="L92">
-        <f>J92-K92</f>
+        <f t="shared" si="3"/>
         <v>157.2944</v>
       </c>
     </row>
@@ -4493,11 +4514,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J93">
-        <f>G93*0.94-H93</f>
+        <f t="shared" si="2"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L93">
-        <f>J93-K93</f>
+        <f t="shared" si="3"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -4530,11 +4551,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J94">
-        <f>G94*0.94-H94</f>
+        <f t="shared" si="2"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L94">
-        <f>J94-K94</f>
+        <f t="shared" si="3"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -4567,11 +4588,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J95">
-        <f>G95*0.94-H95</f>
+        <f t="shared" si="2"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L95">
-        <f>J95-K95</f>
+        <f t="shared" si="3"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -4604,11 +4625,11 @@
         <v>75.512</v>
       </c>
       <c r="J96">
-        <f>G96*0.94-H96</f>
+        <f t="shared" si="2"/>
         <v>69.84859999999999</v>
       </c>
       <c r="L96">
-        <f>J96-K96</f>
+        <f t="shared" si="3"/>
         <v>69.84859999999999</v>
       </c>
     </row>
@@ -4641,11 +4662,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J97">
-        <f>G97*0.94-H97</f>
+        <f t="shared" si="2"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L97">
-        <f>J97-K97</f>
+        <f t="shared" si="3"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -4678,11 +4699,11 @@
         <v>29.6</v>
       </c>
       <c r="J98">
-        <f>G98*0.94-H98</f>
+        <f t="shared" si="2"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L98">
-        <f>J98-K98</f>
+        <f t="shared" si="3"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -4715,11 +4736,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J99">
-        <f>G99*0.94-H99</f>
+        <f t="shared" si="2"/>
         <v>21.2972</v>
       </c>
       <c r="L99">
-        <f>J99-K99</f>
+        <f t="shared" si="3"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -4752,11 +4773,11 @@
         <v>165.93799999999999</v>
       </c>
       <c r="J100">
-        <f>G100*0.94-H100</f>
+        <f t="shared" si="2"/>
         <v>153.49267999999998</v>
       </c>
       <c r="L100">
-        <f>J100-K100</f>
+        <f t="shared" si="3"/>
         <v>153.49267999999998</v>
       </c>
     </row>
@@ -4789,11 +4810,11 @@
         <v>36.015999999999998</v>
       </c>
       <c r="J101">
-        <f>G101*0.94-H101</f>
+        <f t="shared" si="2"/>
         <v>33.314800000000005</v>
       </c>
       <c r="L101">
-        <f>J101-K101</f>
+        <f t="shared" si="3"/>
         <v>33.314800000000005</v>
       </c>
     </row>
@@ -4826,11 +4847,11 @@
         <v>44.031999999999996</v>
       </c>
       <c r="J102">
-        <f>G102*0.94-H102</f>
+        <f t="shared" si="2"/>
         <v>40.729599999999991</v>
       </c>
       <c r="L102">
-        <f>J102-K102</f>
+        <f t="shared" si="3"/>
         <v>40.729599999999991</v>
       </c>
     </row>
@@ -4863,11 +4884,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J103">
-        <f>G103*0.94-H103</f>
+        <f t="shared" si="2"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L103">
-        <f>J103-K103</f>
+        <f t="shared" si="3"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -4900,11 +4921,11 @@
         <v>42.944000000000003</v>
       </c>
       <c r="J104">
-        <f>G104*0.94-H104</f>
+        <f t="shared" si="2"/>
         <v>39.723199999999991</v>
       </c>
       <c r="L104">
-        <f>J104-K104</f>
+        <f t="shared" si="3"/>
         <v>39.723199999999991</v>
       </c>
     </row>
@@ -4937,11 +4958,11 @@
         <v>39.631999999999998</v>
       </c>
       <c r="J105">
-        <f>G105*0.94-H105</f>
+        <f t="shared" si="2"/>
         <v>36.659599999999998</v>
       </c>
       <c r="L105">
-        <f>J105-K105</f>
+        <f t="shared" si="3"/>
         <v>36.659599999999998</v>
       </c>
     </row>
@@ -4974,11 +4995,11 @@
         <v>100.488</v>
       </c>
       <c r="J106">
-        <f>G106*0.94-H106</f>
+        <f t="shared" si="2"/>
         <v>92.951399999999992</v>
       </c>
       <c r="L106">
-        <f>J106-K106</f>
+        <f t="shared" si="3"/>
         <v>92.951399999999992</v>
       </c>
     </row>
@@ -5011,11 +5032,11 @@
         <v>114.31399999999999</v>
       </c>
       <c r="J107">
-        <f>G107*0.94-H107</f>
+        <f t="shared" si="2"/>
         <v>105.74047999999999</v>
       </c>
       <c r="L107">
-        <f>J107-K107</f>
+        <f t="shared" si="3"/>
         <v>105.74047999999999</v>
       </c>
     </row>
@@ -5048,11 +5069,11 @@
         <v>35.344000000000001</v>
       </c>
       <c r="J108">
-        <f>G108*0.94-H108</f>
+        <f t="shared" si="2"/>
         <v>32.693199999999997</v>
       </c>
       <c r="L108">
-        <f>J108-K108</f>
+        <f t="shared" si="3"/>
         <v>32.693199999999997</v>
       </c>
     </row>
@@ -5085,11 +5106,11 @@
         <v>53.368000000000002</v>
       </c>
       <c r="J109">
-        <f>G109*0.94-H109</f>
+        <f t="shared" si="2"/>
         <v>49.365399999999994</v>
       </c>
       <c r="L109">
-        <f>J109-K109</f>
+        <f t="shared" si="3"/>
         <v>49.365399999999994</v>
       </c>
     </row>
@@ -5122,11 +5143,11 @@
         <v>89.53</v>
       </c>
       <c r="J110">
-        <f>G110*0.94-H110</f>
+        <f t="shared" si="2"/>
         <v>82.815280000000001</v>
       </c>
       <c r="L110">
-        <f>J110-K110</f>
+        <f t="shared" si="3"/>
         <v>82.815280000000001</v>
       </c>
     </row>
@@ -5159,11 +5180,11 @@
         <v>30.256</v>
       </c>
       <c r="J111">
-        <f>G111*0.94-H111</f>
+        <f t="shared" si="2"/>
         <v>27.986799999999995</v>
       </c>
       <c r="L111">
-        <f>J111-K111</f>
+        <f t="shared" si="3"/>
         <v>27.986799999999995</v>
       </c>
     </row>
@@ -5196,11 +5217,11 @@
         <v>155.88</v>
       </c>
       <c r="J112">
-        <f>G112*0.94-H112</f>
+        <f t="shared" si="2"/>
         <v>144.18899999999999</v>
       </c>
       <c r="L112">
-        <f>J112-K112</f>
+        <f t="shared" si="3"/>
         <v>144.18899999999999</v>
       </c>
     </row>
@@ -5233,11 +5254,11 @@
         <v>57.552</v>
       </c>
       <c r="J113">
-        <f>G113*0.94-H113</f>
+        <f t="shared" si="2"/>
         <v>53.235599999999998</v>
       </c>
       <c r="L113">
-        <f>J113-K113</f>
+        <f t="shared" si="3"/>
         <v>53.235599999999998</v>
       </c>
     </row>
@@ -5270,11 +5291,11 @@
         <v>45.832000000000001</v>
       </c>
       <c r="J114">
-        <f>G114*0.94-H114</f>
+        <f t="shared" si="2"/>
         <v>42.394599999999997</v>
       </c>
       <c r="L114">
-        <f>J114-K114</f>
+        <f t="shared" si="3"/>
         <v>42.394599999999997</v>
       </c>
     </row>
@@ -5307,11 +5328,11 @@
         <v>70.248000000000005</v>
       </c>
       <c r="J115">
-        <f>G115*0.94-H115</f>
+        <f t="shared" si="2"/>
         <v>64.979399999999998</v>
       </c>
       <c r="L115">
-        <f>J115-K115</f>
+        <f t="shared" si="3"/>
         <v>64.979399999999998</v>
       </c>
     </row>
@@ -5344,11 +5365,11 @@
         <v>35.207999999999998</v>
       </c>
       <c r="J116">
-        <f>G116*0.94-H116</f>
+        <f t="shared" si="2"/>
         <v>32.567399999999999</v>
       </c>
       <c r="L116">
-        <f>J116-K116</f>
+        <f t="shared" si="3"/>
         <v>32.567399999999999</v>
       </c>
     </row>
@@ -5381,11 +5402,11 @@
         <v>36.200000000000003</v>
       </c>
       <c r="J117">
-        <f>G117*0.94-H117</f>
+        <f t="shared" si="2"/>
         <v>33.484999999999999</v>
       </c>
       <c r="L117">
-        <f>J117-K117</f>
+        <f t="shared" si="3"/>
         <v>33.484999999999999</v>
       </c>
     </row>
@@ -5418,11 +5439,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J118">
-        <f>G118*0.94-H118</f>
+        <f t="shared" si="2"/>
         <v>21.2972</v>
       </c>
       <c r="L118">
-        <f>J118-K118</f>
+        <f t="shared" si="3"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -5455,11 +5476,11 @@
         <v>158.477</v>
       </c>
       <c r="J119">
-        <f>G119*0.94-H119</f>
+        <f t="shared" si="2"/>
         <v>146.59124</v>
       </c>
       <c r="L119">
-        <f>J119-K119</f>
+        <f t="shared" si="3"/>
         <v>146.59124</v>
       </c>
     </row>
@@ -5492,11 +5513,11 @@
         <v>28.783999999999999</v>
       </c>
       <c r="J120">
-        <f>G120*0.94-H120</f>
+        <f t="shared" si="2"/>
         <v>26.6252</v>
       </c>
       <c r="L120">
-        <f>J120-K120</f>
+        <f t="shared" si="3"/>
         <v>26.6252</v>
       </c>
     </row>
@@ -5529,11 +5550,11 @@
         <v>38.72</v>
       </c>
       <c r="J121">
-        <f>G121*0.94-H121</f>
+        <f t="shared" si="2"/>
         <v>35.815999999999995</v>
       </c>
       <c r="L121">
-        <f>J121-K121</f>
+        <f t="shared" si="3"/>
         <v>35.815999999999995</v>
       </c>
     </row>
@@ -5566,11 +5587,11 @@
         <v>28.984000000000002</v>
       </c>
       <c r="J122">
-        <f>G122*0.94-H122</f>
+        <f t="shared" si="2"/>
         <v>26.810199999999995</v>
       </c>
       <c r="L122">
-        <f>J122-K122</f>
+        <f t="shared" si="3"/>
         <v>26.810199999999995</v>
       </c>
     </row>
@@ -5603,11 +5624,11 @@
         <v>29.135999999999999</v>
       </c>
       <c r="J123">
-        <f>G123*0.94-H123</f>
+        <f t="shared" si="2"/>
         <v>26.950800000000001</v>
       </c>
       <c r="L123">
-        <f>J123-K123</f>
+        <f t="shared" si="3"/>
         <v>26.950800000000001</v>
       </c>
     </row>
@@ -5640,11 +5661,11 @@
         <v>91.176000000000002</v>
       </c>
       <c r="J124">
-        <f>G124*0.94-H124</f>
+        <f t="shared" si="2"/>
         <v>84.337800000000001</v>
       </c>
       <c r="L124">
-        <f>J124-K124</f>
+        <f t="shared" si="3"/>
         <v>84.337800000000001</v>
       </c>
     </row>
@@ -5677,11 +5698,11 @@
         <v>114.41</v>
       </c>
       <c r="J125">
-        <f>G125*0.94-H125</f>
+        <f t="shared" si="2"/>
         <v>105.82927999999998</v>
       </c>
       <c r="L125">
-        <f>J125-K125</f>
+        <f t="shared" si="3"/>
         <v>105.82927999999998</v>
       </c>
     </row>
@@ -5714,11 +5735,11 @@
         <v>35.344000000000001</v>
       </c>
       <c r="J126">
-        <f>G126*0.94-H126</f>
+        <f t="shared" si="2"/>
         <v>32.693199999999997</v>
       </c>
       <c r="L126">
-        <f>J126-K126</f>
+        <f t="shared" si="3"/>
         <v>32.693199999999997</v>
       </c>
     </row>
@@ -5751,11 +5772,11 @@
         <v>53.368000000000002</v>
       </c>
       <c r="J127">
-        <f>G127*0.94-H127</f>
+        <f t="shared" si="2"/>
         <v>49.365399999999994</v>
       </c>
       <c r="L127">
-        <f>J127-K127</f>
+        <f t="shared" si="3"/>
         <v>49.365399999999994</v>
       </c>
     </row>
@@ -5788,11 +5809,11 @@
         <v>102.61</v>
       </c>
       <c r="J128">
-        <f>G128*0.94-H128</f>
+        <f t="shared" si="2"/>
         <v>94.914279999999991</v>
       </c>
       <c r="L128">
-        <f>J128-K128</f>
+        <f t="shared" si="3"/>
         <v>94.914279999999991</v>
       </c>
     </row>
@@ -5825,11 +5846,11 @@
         <v>15.423999999999999</v>
       </c>
       <c r="J129">
-        <f>G129*0.94-H129</f>
+        <f t="shared" si="2"/>
         <v>14.267200000000001</v>
       </c>
       <c r="L129">
-        <f>J129-K129</f>
+        <f t="shared" si="3"/>
         <v>14.267200000000001</v>
       </c>
     </row>
@@ -5862,11 +5883,11 @@
         <v>15.352</v>
       </c>
       <c r="J130">
-        <f>G130*0.94-H130</f>
+        <f t="shared" ref="J130:J193" si="4">G130*0.94-H130</f>
         <v>14.200599999999998</v>
       </c>
       <c r="L130">
-        <f>J130-K130</f>
+        <f t="shared" ref="L130:L193" si="5">J130-K130</f>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -5899,11 +5920,11 @@
         <v>75.256</v>
       </c>
       <c r="J131">
-        <f>G131*0.94-H131</f>
+        <f t="shared" si="4"/>
         <v>69.611799999999988</v>
       </c>
       <c r="L131">
-        <f>J131-K131</f>
+        <f t="shared" si="5"/>
         <v>69.611799999999988</v>
       </c>
     </row>
@@ -5936,11 +5957,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J132">
-        <f>G132*0.94-H132</f>
+        <f t="shared" si="4"/>
         <v>149.99059999999997</v>
       </c>
       <c r="L132">
-        <f>J132-K132</f>
+        <f t="shared" si="5"/>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -5973,11 +5994,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J133">
-        <f>G133*0.94-H133</f>
+        <f t="shared" si="4"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L133">
-        <f>J133-K133</f>
+        <f t="shared" si="5"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -6010,11 +6031,11 @@
         <v>55.671999999999997</v>
       </c>
       <c r="J134">
-        <f>G134*0.94-H134</f>
+        <f t="shared" si="4"/>
         <v>51.496599999999994</v>
       </c>
       <c r="L134">
-        <f>J134-K134</f>
+        <f t="shared" si="5"/>
         <v>51.496599999999994</v>
       </c>
     </row>
@@ -6047,11 +6068,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J135">
-        <f>G135*0.94-H135</f>
+        <f t="shared" si="4"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L135">
-        <f>J135-K135</f>
+        <f t="shared" si="5"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -6084,11 +6105,11 @@
         <v>23.152000000000001</v>
       </c>
       <c r="J136">
-        <f>G136*0.94-H136</f>
+        <f t="shared" si="4"/>
         <v>21.415599999999998</v>
       </c>
       <c r="L136">
-        <f>J136-K136</f>
+        <f t="shared" si="5"/>
         <v>21.415599999999998</v>
       </c>
     </row>
@@ -6121,11 +6142,11 @@
         <v>29.6</v>
       </c>
       <c r="J137">
-        <f>G137*0.94-H137</f>
+        <f t="shared" si="4"/>
         <v>27.380000000000003</v>
       </c>
       <c r="L137">
-        <f>J137-K137</f>
+        <f t="shared" si="5"/>
         <v>27.380000000000003</v>
       </c>
     </row>
@@ -6158,11 +6179,11 @@
         <v>35.287999999999997</v>
       </c>
       <c r="J138">
-        <f>G138*0.94-H138</f>
+        <f t="shared" si="4"/>
         <v>32.641400000000004</v>
       </c>
       <c r="L138">
-        <f>J138-K138</f>
+        <f t="shared" si="5"/>
         <v>32.641400000000004</v>
       </c>
     </row>
@@ -6195,11 +6216,11 @@
         <v>23.024000000000001</v>
       </c>
       <c r="J139">
-        <f>G139*0.94-H139</f>
+        <f t="shared" si="4"/>
         <v>21.2972</v>
       </c>
       <c r="L139">
-        <f>J139-K139</f>
+        <f t="shared" si="5"/>
         <v>21.2972</v>
       </c>
     </row>
@@ -6232,11 +6253,11 @@
         <v>165.93799999999999</v>
       </c>
       <c r="J140">
-        <f>G140*0.94-H140</f>
+        <f t="shared" si="4"/>
         <v>153.49267999999998</v>
       </c>
       <c r="L140">
-        <f>J140-K140</f>
+        <f t="shared" si="5"/>
         <v>153.49267999999998</v>
       </c>
     </row>
@@ -6269,11 +6290,11 @@
         <v>35.128</v>
       </c>
       <c r="J141">
-        <f>G141*0.94-H141</f>
+        <f t="shared" si="4"/>
         <v>32.493399999999994</v>
       </c>
       <c r="L141">
-        <f>J141-K141</f>
+        <f t="shared" si="5"/>
         <v>32.493399999999994</v>
       </c>
     </row>
@@ -6306,11 +6327,11 @@
         <v>8.8160000000000007</v>
       </c>
       <c r="J142">
-        <f>G142*0.94-H142</f>
+        <f t="shared" si="4"/>
         <v>8.1547999999999981</v>
       </c>
       <c r="L142">
-        <f>J142-K142</f>
+        <f t="shared" si="5"/>
         <v>8.1547999999999981</v>
       </c>
     </row>
@@ -6343,11 +6364,11 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="J143">
-        <f>G143*0.94-H143</f>
+        <f t="shared" si="4"/>
         <v>2.0719999999999996</v>
       </c>
       <c r="L143">
-        <f>J143-K143</f>
+        <f t="shared" si="5"/>
         <v>2.0719999999999996</v>
       </c>
     </row>
@@ -6380,11 +6401,11 @@
         <v>25.783999999999999</v>
       </c>
       <c r="J144">
-        <f>G144*0.94-H144</f>
+        <f t="shared" si="4"/>
         <v>23.850199999999994</v>
       </c>
       <c r="L144">
-        <f>J144-K144</f>
+        <f t="shared" si="5"/>
         <v>23.850199999999994</v>
       </c>
     </row>
@@ -6417,11 +6438,11 @@
         <v>21.872</v>
       </c>
       <c r="J145">
-        <f>G145*0.94-H145</f>
+        <f t="shared" si="4"/>
         <v>20.231599999999997</v>
       </c>
       <c r="L145">
-        <f>J145-K145</f>
+        <f t="shared" si="5"/>
         <v>20.231599999999997</v>
       </c>
     </row>
@@ -6454,11 +6475,11 @@
         <v>94.512</v>
       </c>
       <c r="J146">
-        <f>G146*0.94-H146</f>
+        <f t="shared" si="4"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L146">
-        <f>J146-K146</f>
+        <f t="shared" si="5"/>
         <v>87.423599999999993</v>
       </c>
     </row>
@@ -6491,11 +6512,11 @@
         <v>117.378</v>
       </c>
       <c r="J147">
-        <f>G147*0.94-H147</f>
+        <f t="shared" si="4"/>
         <v>108.57468</v>
       </c>
       <c r="L147">
-        <f>J147-K147</f>
+        <f t="shared" si="5"/>
         <v>108.57468</v>
       </c>
     </row>
@@ -6528,11 +6549,11 @@
         <v>54.295999999999999</v>
       </c>
       <c r="J148">
-        <f>G148*0.94-H148</f>
+        <f t="shared" si="4"/>
         <v>50.223800000000004</v>
       </c>
       <c r="L148">
-        <f>J148-K148</f>
+        <f t="shared" si="5"/>
         <v>50.223800000000004</v>
       </c>
     </row>
@@ -6565,11 +6586,11 @@
         <v>89.53</v>
       </c>
       <c r="J149">
-        <f>G149*0.94-H149</f>
+        <f t="shared" si="4"/>
         <v>82.815280000000001</v>
       </c>
       <c r="L149">
-        <f>J149-K149</f>
+        <f t="shared" si="5"/>
         <v>82.815280000000001</v>
       </c>
     </row>
@@ -6602,11 +6623,11 @@
         <v>9.4480000000000004</v>
       </c>
       <c r="J150">
-        <f>G150*0.94-H150</f>
+        <f t="shared" si="4"/>
         <v>8.7393999999999998</v>
       </c>
       <c r="L150">
-        <f>J150-K150</f>
+        <f t="shared" si="5"/>
         <v>8.7393999999999998</v>
       </c>
     </row>
@@ -6639,11 +6660,11 @@
         <v>15.352</v>
       </c>
       <c r="J151">
-        <f>G151*0.94-H151</f>
+        <f t="shared" si="4"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L151">
-        <f>J151-K151</f>
+        <f t="shared" si="5"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -6676,11 +6697,11 @@
         <v>70.712000000000003</v>
       </c>
       <c r="J152">
-        <f>G152*0.94-H152</f>
+        <f t="shared" si="4"/>
         <v>65.408599999999993</v>
       </c>
       <c r="L152">
-        <f>J152-K152</f>
+        <f t="shared" si="5"/>
         <v>65.408599999999993</v>
       </c>
     </row>
@@ -6713,11 +6734,11 @@
         <v>35.344000000000001</v>
       </c>
       <c r="J153">
-        <f>G153*0.94-H153</f>
+        <f t="shared" si="4"/>
         <v>32.693199999999997</v>
       </c>
       <c r="L153">
-        <f>J153-K153</f>
+        <f t="shared" si="5"/>
         <v>32.693199999999997</v>
       </c>
     </row>
@@ -6750,11 +6771,11 @@
         <v>162.15199999999999</v>
       </c>
       <c r="J154">
-        <f>G154*0.94-H154</f>
+        <f t="shared" si="4"/>
         <v>149.99059999999997</v>
       </c>
       <c r="L154">
-        <f>J154-K154</f>
+        <f t="shared" si="5"/>
         <v>149.99059999999997</v>
       </c>
     </row>
@@ -6787,11 +6808,11 @@
         <v>47.4</v>
       </c>
       <c r="J155">
-        <f>G155*0.94-H155</f>
+        <f t="shared" si="4"/>
         <v>43.844999999999999</v>
       </c>
       <c r="L155">
-        <f>J155-K155</f>
+        <f t="shared" si="5"/>
         <v>43.844999999999999</v>
       </c>
     </row>
@@ -6824,11 +6845,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J156">
-        <f>G156*0.94-H156</f>
+        <f t="shared" si="4"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L156">
-        <f>J156-K156</f>
+        <f t="shared" si="5"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -6861,11 +6882,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J157">
-        <f>G157*0.94-H157</f>
+        <f t="shared" si="4"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L157">
-        <f>J157-K157</f>
+        <f t="shared" si="5"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -6898,11 +6919,11 @@
         <v>35.543999999999997</v>
       </c>
       <c r="J158">
-        <f>G158*0.94-H158</f>
+        <f t="shared" si="4"/>
         <v>32.878199999999993</v>
       </c>
       <c r="L158">
-        <f>J158-K158</f>
+        <f t="shared" si="5"/>
         <v>32.878199999999993</v>
       </c>
     </row>
@@ -6935,11 +6956,11 @@
         <v>36.456000000000003</v>
       </c>
       <c r="J159">
-        <f>G159*0.94-H159</f>
+        <f t="shared" si="4"/>
         <v>33.721800000000002</v>
       </c>
       <c r="L159">
-        <f>J159-K159</f>
+        <f t="shared" si="5"/>
         <v>33.721800000000002</v>
       </c>
     </row>
@@ -6972,11 +6993,11 @@
         <v>35.287999999999997</v>
       </c>
       <c r="J160">
-        <f>G160*0.94-H160</f>
+        <f t="shared" si="4"/>
         <v>32.641400000000004</v>
       </c>
       <c r="L160">
-        <f>J160-K160</f>
+        <f t="shared" si="5"/>
         <v>32.641400000000004</v>
       </c>
     </row>
@@ -7009,11 +7030,11 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J161">
-        <f>G161*0.94-H161</f>
+        <f t="shared" si="4"/>
         <v>28.297599999999999</v>
       </c>
       <c r="L161">
-        <f>J161-K161</f>
+        <f t="shared" si="5"/>
         <v>28.297599999999999</v>
       </c>
     </row>
@@ -7046,11 +7067,11 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J162">
-        <f>G162*0.94-H162</f>
+        <f t="shared" si="4"/>
         <v>22.1038</v>
       </c>
       <c r="L162">
-        <f>J162-K162</f>
+        <f t="shared" si="5"/>
         <v>22.1038</v>
       </c>
     </row>
@@ -7083,11 +7104,11 @@
         <v>193.09</v>
       </c>
       <c r="J163">
-        <f>G163*0.94-H163</f>
+        <f t="shared" si="4"/>
         <v>178.60827999999998</v>
       </c>
       <c r="L163">
-        <f>J163-K163</f>
+        <f t="shared" si="5"/>
         <v>178.60827999999998</v>
       </c>
     </row>
@@ -7120,11 +7141,11 @@
         <v>46.456000000000003</v>
       </c>
       <c r="J164">
-        <f>G164*0.94-H164</f>
+        <f t="shared" si="4"/>
         <v>42.971800000000002</v>
       </c>
       <c r="L164">
-        <f>J164-K164</f>
+        <f t="shared" si="5"/>
         <v>42.971800000000002</v>
       </c>
     </row>
@@ -7157,11 +7178,11 @@
         <v>25.968</v>
       </c>
       <c r="J165">
-        <f>G165*0.94-H165</f>
+        <f t="shared" si="4"/>
         <v>24.020399999999999</v>
       </c>
       <c r="L165">
-        <f>J165-K165</f>
+        <f t="shared" si="5"/>
         <v>24.020399999999999</v>
       </c>
     </row>
@@ -7194,11 +7215,11 @@
         <v>49.856000000000002</v>
       </c>
       <c r="J166">
-        <f>G166*0.94-H166</f>
+        <f t="shared" si="4"/>
         <v>46.116799999999998</v>
       </c>
       <c r="L166">
-        <f>J166-K166</f>
+        <f t="shared" si="5"/>
         <v>46.116799999999998</v>
       </c>
     </row>
@@ -7231,11 +7252,11 @@
         <v>29.495999999999999</v>
       </c>
       <c r="J167">
-        <f>G167*0.94-H167</f>
+        <f t="shared" si="4"/>
         <v>27.283799999999996</v>
       </c>
       <c r="L167">
-        <f>J167-K167</f>
+        <f t="shared" si="5"/>
         <v>27.283799999999996</v>
       </c>
     </row>
@@ -7268,11 +7289,11 @@
         <v>38.456000000000003</v>
       </c>
       <c r="J168">
-        <f>G168*0.94-H168</f>
+        <f t="shared" si="4"/>
         <v>35.571799999999996</v>
       </c>
       <c r="L168">
-        <f>J168-K168</f>
+        <f t="shared" si="5"/>
         <v>35.571799999999996</v>
       </c>
     </row>
@@ -7305,11 +7326,11 @@
         <v>46.335999999999999</v>
       </c>
       <c r="J169">
-        <f>G169*0.94-H169</f>
+        <f t="shared" si="4"/>
         <v>42.860799999999998</v>
       </c>
       <c r="L169">
-        <f>J169-K169</f>
+        <f t="shared" si="5"/>
         <v>42.860799999999998</v>
       </c>
     </row>
@@ -7342,11 +7363,11 @@
         <v>46.863999999999997</v>
       </c>
       <c r="J170">
-        <f>G170*0.94-H170</f>
+        <f t="shared" si="4"/>
         <v>43.349199999999996</v>
       </c>
       <c r="L170">
-        <f>J170-K170</f>
+        <f t="shared" si="5"/>
         <v>43.349199999999996</v>
       </c>
     </row>
@@ -7379,11 +7400,11 @@
         <v>94.512</v>
       </c>
       <c r="J171">
-        <f>G171*0.94-H171</f>
+        <f t="shared" si="4"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L171">
-        <f>J171-K171</f>
+        <f t="shared" si="5"/>
         <v>87.423599999999993</v>
       </c>
     </row>
@@ -7416,11 +7437,11 @@
         <v>110.17</v>
       </c>
       <c r="J172">
-        <f>G172*0.94-H172</f>
+        <f t="shared" si="4"/>
         <v>101.90727999999999</v>
       </c>
       <c r="L172">
-        <f>J172-K172</f>
+        <f t="shared" si="5"/>
         <v>101.90727999999999</v>
       </c>
     </row>
@@ -7453,11 +7474,11 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J173">
-        <f>G173*0.94-H173</f>
+        <f t="shared" si="4"/>
         <v>33.4998</v>
       </c>
       <c r="L173">
-        <f>J173-K173</f>
+        <f t="shared" si="5"/>
         <v>33.4998</v>
       </c>
     </row>
@@ -7490,11 +7511,11 @@
         <v>90.097999999999999</v>
       </c>
       <c r="J174">
-        <f>G174*0.94-H174</f>
+        <f t="shared" si="4"/>
         <v>83.340679999999992</v>
       </c>
       <c r="L174">
-        <f>J174-K174</f>
+        <f t="shared" si="5"/>
         <v>83.340679999999992</v>
       </c>
     </row>
@@ -7527,11 +7548,11 @@
         <v>50.52</v>
       </c>
       <c r="J175">
-        <f>G175*0.94-H175</f>
+        <f t="shared" si="4"/>
         <v>46.730999999999995</v>
       </c>
       <c r="L175">
-        <f>J175-K175</f>
+        <f t="shared" si="5"/>
         <v>46.730999999999995</v>
       </c>
     </row>
@@ -7564,11 +7585,11 @@
         <v>40.573999999999998</v>
       </c>
       <c r="J176">
-        <f>G176*0.94-H176</f>
+        <f t="shared" si="4"/>
         <v>37.530979999999992</v>
       </c>
       <c r="L176">
-        <f>J176-K176</f>
+        <f t="shared" si="5"/>
         <v>37.530979999999992</v>
       </c>
     </row>
@@ -7601,11 +7622,11 @@
         <v>43.503999999999998</v>
       </c>
       <c r="J177">
-        <f>G177*0.94-H177</f>
+        <f t="shared" si="4"/>
         <v>40.241199999999999</v>
       </c>
       <c r="L177">
-        <f>J177-K177</f>
+        <f t="shared" si="5"/>
         <v>40.241199999999999</v>
       </c>
     </row>
@@ -7638,11 +7659,11 @@
         <v>9.68</v>
       </c>
       <c r="J178">
-        <f>G178*0.94-H178</f>
+        <f t="shared" si="4"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="L178">
-        <f>J178-K178</f>
+        <f t="shared" si="5"/>
         <v>8.9539999999999988</v>
       </c>
     </row>
@@ -7675,11 +7696,11 @@
         <v>20.143999999999998</v>
       </c>
       <c r="J179">
-        <f>G179*0.94-H179</f>
+        <f t="shared" si="4"/>
         <v>18.633200000000002</v>
       </c>
       <c r="L179">
-        <f>J179-K179</f>
+        <f t="shared" si="5"/>
         <v>18.633200000000002</v>
       </c>
     </row>
@@ -7712,11 +7733,11 @@
         <v>70.712000000000003</v>
       </c>
       <c r="J180">
-        <f>G180*0.94-H180</f>
+        <f t="shared" si="4"/>
         <v>65.408599999999993</v>
       </c>
       <c r="L180">
-        <f>J180-K180</f>
+        <f t="shared" si="5"/>
         <v>65.408599999999993</v>
       </c>
     </row>
@@ -7749,11 +7770,11 @@
         <v>163.608</v>
       </c>
       <c r="J181">
-        <f>G181*0.94-H181</f>
+        <f t="shared" si="4"/>
         <v>151.3374</v>
       </c>
       <c r="L181">
-        <f>J181-K181</f>
+        <f t="shared" si="5"/>
         <v>151.3374</v>
       </c>
     </row>
@@ -7786,11 +7807,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J182">
-        <f>G182*0.94-H182</f>
+        <f t="shared" si="4"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L182">
-        <f>J182-K182</f>
+        <f t="shared" si="5"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -7823,11 +7844,11 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J183">
-        <f>G183*0.94-H183</f>
+        <f t="shared" si="4"/>
         <v>44.38519999999999</v>
       </c>
       <c r="L183">
-        <f>J183-K183</f>
+        <f t="shared" si="5"/>
         <v>44.38519999999999</v>
       </c>
     </row>
@@ -7860,11 +7881,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J184">
-        <f>G184*0.94-H184</f>
+        <f t="shared" si="4"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L184">
-        <f>J184-K184</f>
+        <f t="shared" si="5"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -7897,11 +7918,11 @@
         <v>160.02099999999999</v>
       </c>
       <c r="J185">
-        <f>G185*0.94-H185</f>
+        <f t="shared" si="4"/>
         <v>148.01944</v>
       </c>
       <c r="L185">
-        <f>J185-K185</f>
+        <f t="shared" si="5"/>
         <v>148.01944</v>
       </c>
     </row>
@@ -7934,11 +7955,11 @@
         <v>35.872</v>
       </c>
       <c r="J186">
-        <f>G186*0.94-H186</f>
+        <f t="shared" si="4"/>
         <v>33.181600000000003</v>
       </c>
       <c r="L186">
-        <f>J186-K186</f>
+        <f t="shared" si="5"/>
         <v>33.181600000000003</v>
       </c>
     </row>
@@ -7971,11 +7992,11 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J187">
-        <f>G187*0.94-H187</f>
+        <f t="shared" si="4"/>
         <v>28.297599999999999</v>
       </c>
       <c r="L187">
-        <f>J187-K187</f>
+        <f t="shared" si="5"/>
         <v>28.297599999999999</v>
       </c>
     </row>
@@ -8008,11 +8029,11 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J188">
-        <f>G188*0.94-H188</f>
+        <f t="shared" si="4"/>
         <v>22.1038</v>
       </c>
       <c r="L188">
-        <f>J188-K188</f>
+        <f t="shared" si="5"/>
         <v>22.1038</v>
       </c>
     </row>
@@ -8045,11 +8066,11 @@
         <v>21.968</v>
       </c>
       <c r="J189">
-        <f>G189*0.94-H189</f>
+        <f t="shared" si="4"/>
         <v>20.320399999999999</v>
       </c>
       <c r="L189">
-        <f>J189-K189</f>
+        <f t="shared" si="5"/>
         <v>20.320399999999999</v>
       </c>
     </row>
@@ -8082,11 +8103,11 @@
         <v>40.847999999999999</v>
       </c>
       <c r="J190">
-        <f>G190*0.94-H190</f>
+        <f t="shared" si="4"/>
         <v>37.784400000000005</v>
       </c>
       <c r="L190">
-        <f>J190-K190</f>
+        <f t="shared" si="5"/>
         <v>37.784400000000005</v>
       </c>
     </row>
@@ -8119,11 +8140,11 @@
         <v>94.512</v>
       </c>
       <c r="J191">
-        <f>G191*0.94-H191</f>
+        <f t="shared" si="4"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L191">
-        <f>J191-K191</f>
+        <f t="shared" si="5"/>
         <v>87.423599999999993</v>
       </c>
     </row>
@@ -8156,11 +8177,11 @@
         <v>114.97799999999999</v>
       </c>
       <c r="J192">
-        <f>G192*0.94-H192</f>
+        <f t="shared" si="4"/>
         <v>106.35468</v>
       </c>
       <c r="L192">
-        <f>J192-K192</f>
+        <f t="shared" si="5"/>
         <v>106.35468</v>
       </c>
     </row>
@@ -8193,11 +8214,11 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J193">
-        <f>G193*0.94-H193</f>
+        <f t="shared" si="4"/>
         <v>33.4998</v>
       </c>
       <c r="L193">
-        <f>J193-K193</f>
+        <f t="shared" si="5"/>
         <v>33.4998</v>
       </c>
     </row>
@@ -8230,11 +8251,11 @@
         <v>90.097999999999999</v>
       </c>
       <c r="J194">
-        <f>G194*0.94-H194</f>
+        <f t="shared" ref="J194:J257" si="6">G194*0.94-H194</f>
         <v>83.340679999999992</v>
       </c>
       <c r="L194">
-        <f>J194-K194</f>
+        <f t="shared" ref="L194:L257" si="7">J194-K194</f>
         <v>83.340679999999992</v>
       </c>
     </row>
@@ -8267,11 +8288,11 @@
         <v>9.68</v>
       </c>
       <c r="J195">
-        <f>G195*0.94-H195</f>
+        <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="L195">
-        <f>J195-K195</f>
+        <f t="shared" si="7"/>
         <v>8.9539999999999988</v>
       </c>
     </row>
@@ -8304,11 +8325,11 @@
         <v>15.352</v>
       </c>
       <c r="J196">
-        <f>G196*0.94-H196</f>
+        <f t="shared" si="6"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L196">
-        <f>J196-K196</f>
+        <f t="shared" si="7"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -8341,11 +8362,11 @@
         <v>70.712000000000003</v>
       </c>
       <c r="J197">
-        <f>G197*0.94-H197</f>
+        <f t="shared" si="6"/>
         <v>65.408599999999993</v>
       </c>
       <c r="L197">
-        <f>J197-K197</f>
+        <f t="shared" si="7"/>
         <v>65.408599999999993</v>
       </c>
     </row>
@@ -8378,11 +8399,11 @@
         <v>163.608</v>
       </c>
       <c r="J198">
-        <f>G198*0.94-H198</f>
+        <f t="shared" si="6"/>
         <v>151.3374</v>
       </c>
       <c r="L198">
-        <f>J198-K198</f>
+        <f t="shared" si="7"/>
         <v>151.3374</v>
       </c>
     </row>
@@ -8415,11 +8436,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J199">
-        <f>G199*0.94-H199</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L199">
-        <f>J199-K199</f>
+        <f t="shared" si="7"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -8452,11 +8473,11 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J200">
-        <f>G200*0.94-H200</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="L200">
-        <f>J200-K200</f>
+        <f t="shared" si="7"/>
         <v>44.38519999999999</v>
       </c>
     </row>
@@ -8489,11 +8510,11 @@
         <v>66.072000000000003</v>
       </c>
       <c r="J201">
-        <f>G201*0.94-H201</f>
+        <f t="shared" si="6"/>
         <v>61.116599999999991</v>
       </c>
       <c r="L201">
-        <f>J201-K201</f>
+        <f t="shared" si="7"/>
         <v>61.116599999999991</v>
       </c>
     </row>
@@ -8526,11 +8547,11 @@
         <v>45.176000000000002</v>
       </c>
       <c r="J202">
-        <f>G202*0.94-H202</f>
+        <f t="shared" si="6"/>
         <v>41.78779999999999</v>
       </c>
       <c r="L202">
-        <f>J202-K202</f>
+        <f t="shared" si="7"/>
         <v>41.78779999999999</v>
       </c>
     </row>
@@ -8563,11 +8584,11 @@
         <v>42.247999999999998</v>
       </c>
       <c r="J203">
-        <f>G203*0.94-H203</f>
+        <f t="shared" si="6"/>
         <v>39.0794</v>
       </c>
       <c r="L203">
-        <f>J203-K203</f>
+        <f t="shared" si="7"/>
         <v>39.0794</v>
       </c>
     </row>
@@ -8600,11 +8621,11 @@
         <v>38.584000000000003</v>
       </c>
       <c r="J204">
-        <f>G204*0.94-H204</f>
+        <f t="shared" si="6"/>
         <v>35.69019999999999</v>
       </c>
       <c r="L204">
-        <f>J204-K204</f>
+        <f t="shared" si="7"/>
         <v>35.69019999999999</v>
       </c>
     </row>
@@ -8637,11 +8658,11 @@
         <v>167.482</v>
       </c>
       <c r="J205">
-        <f>G205*0.94-H205</f>
+        <f t="shared" si="6"/>
         <v>154.92087999999998</v>
       </c>
       <c r="L205">
-        <f>J205-K205</f>
+        <f t="shared" si="7"/>
         <v>154.92087999999998</v>
       </c>
     </row>
@@ -8674,11 +8695,11 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J206">
-        <f>G206*0.94-H206</f>
+        <f t="shared" si="6"/>
         <v>28.297599999999999</v>
       </c>
       <c r="L206">
-        <f>J206-K206</f>
+        <f t="shared" si="7"/>
         <v>28.297599999999999</v>
       </c>
     </row>
@@ -8711,11 +8732,11 @@
         <v>33.536000000000001</v>
       </c>
       <c r="J207">
-        <f>G207*0.94-H207</f>
+        <f t="shared" si="6"/>
         <v>31.020800000000001</v>
       </c>
       <c r="L207">
-        <f>J207-K207</f>
+        <f t="shared" si="7"/>
         <v>31.020800000000001</v>
       </c>
     </row>
@@ -8748,11 +8769,11 @@
         <v>35.872</v>
       </c>
       <c r="J208">
-        <f>G208*0.94-H208</f>
+        <f t="shared" si="6"/>
         <v>33.181600000000003</v>
       </c>
       <c r="L208">
-        <f>J208-K208</f>
+        <f t="shared" si="7"/>
         <v>33.181600000000003</v>
       </c>
     </row>
@@ -8785,11 +8806,11 @@
         <v>44.872</v>
       </c>
       <c r="J209">
-        <f>G209*0.94-H209</f>
+        <f t="shared" si="6"/>
         <v>41.506600000000006</v>
       </c>
       <c r="L209">
-        <f>J209-K209</f>
+        <f t="shared" si="7"/>
         <v>41.506600000000006</v>
       </c>
     </row>
@@ -8822,11 +8843,11 @@
         <v>40.024000000000001</v>
       </c>
       <c r="J210">
-        <f>G210*0.94-H210</f>
+        <f t="shared" si="6"/>
         <v>37.022199999999998</v>
       </c>
       <c r="L210">
-        <f>J210-K210</f>
+        <f t="shared" si="7"/>
         <v>37.022199999999998</v>
       </c>
     </row>
@@ -8859,11 +8880,11 @@
         <v>41.287999999999997</v>
       </c>
       <c r="J211">
-        <f>G211*0.94-H211</f>
+        <f t="shared" si="6"/>
         <v>38.191400000000002</v>
       </c>
       <c r="L211">
-        <f>J211-K211</f>
+        <f t="shared" si="7"/>
         <v>38.191400000000002</v>
       </c>
     </row>
@@ -8896,11 +8917,11 @@
         <v>44.488</v>
       </c>
       <c r="J212">
-        <f>G212*0.94-H212</f>
+        <f t="shared" si="6"/>
         <v>41.151399999999995</v>
       </c>
       <c r="L212">
-        <f>J212-K212</f>
+        <f t="shared" si="7"/>
         <v>41.151399999999995</v>
       </c>
     </row>
@@ -8933,11 +8954,11 @@
         <v>39.863999999999997</v>
       </c>
       <c r="J213">
-        <f>G213*0.94-H213</f>
+        <f t="shared" si="6"/>
         <v>36.874199999999995</v>
       </c>
       <c r="L213">
-        <f>J213-K213</f>
+        <f t="shared" si="7"/>
         <v>36.874199999999995</v>
       </c>
     </row>
@@ -8970,11 +8991,11 @@
         <v>20.975999999999999</v>
       </c>
       <c r="J214">
-        <f>G214*0.94-H214</f>
+        <f t="shared" si="6"/>
         <v>19.402799999999999</v>
       </c>
       <c r="L214">
-        <f>J214-K214</f>
+        <f t="shared" si="7"/>
         <v>19.402799999999999</v>
       </c>
     </row>
@@ -9007,11 +9028,11 @@
         <v>114.146</v>
       </c>
       <c r="J215">
-        <f>G215*0.94-H215</f>
+        <f t="shared" si="6"/>
         <v>105.58507999999998</v>
       </c>
       <c r="L215">
-        <f>J215-K215</f>
+        <f t="shared" si="7"/>
         <v>105.58507999999998</v>
       </c>
     </row>
@@ -9044,11 +9065,11 @@
         <v>94.512</v>
       </c>
       <c r="J216">
-        <f>G216*0.94-H216</f>
+        <f t="shared" si="6"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L216">
-        <f>J216-K216</f>
+        <f t="shared" si="7"/>
         <v>87.423599999999993</v>
       </c>
     </row>
@@ -9081,11 +9102,11 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J217">
-        <f>G217*0.94-H217</f>
+        <f t="shared" si="6"/>
         <v>33.4998</v>
       </c>
       <c r="L217">
-        <f>J217-K217</f>
+        <f t="shared" si="7"/>
         <v>33.4998</v>
       </c>
     </row>
@@ -9118,11 +9139,11 @@
         <v>95.29</v>
       </c>
       <c r="J218">
-        <f>G218*0.94-H218</f>
+        <f t="shared" si="6"/>
         <v>88.14327999999999</v>
       </c>
       <c r="L218">
-        <f>J218-K218</f>
+        <f t="shared" si="7"/>
         <v>88.14327999999999</v>
       </c>
     </row>
@@ -9155,11 +9176,11 @@
         <v>9.68</v>
       </c>
       <c r="J219">
-        <f>G219*0.94-H219</f>
+        <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="L219">
-        <f>J219-K219</f>
+        <f t="shared" si="7"/>
         <v>8.9539999999999988</v>
       </c>
     </row>
@@ -9192,11 +9213,11 @@
         <v>15.352</v>
       </c>
       <c r="J220">
-        <f>G220*0.94-H220</f>
+        <f t="shared" si="6"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L220">
-        <f>J220-K220</f>
+        <f t="shared" si="7"/>
         <v>14.200599999999998</v>
       </c>
     </row>
@@ -9229,11 +9250,11 @@
         <v>122.55200000000001</v>
       </c>
       <c r="J221">
-        <f>G221*0.94-H221</f>
+        <f t="shared" si="6"/>
         <v>113.36059999999998</v>
       </c>
       <c r="L221">
-        <f>J221-K221</f>
+        <f t="shared" si="7"/>
         <v>113.36059999999998</v>
       </c>
     </row>
@@ -9266,11 +9287,11 @@
         <v>164.15199999999999</v>
       </c>
       <c r="J222">
-        <f>G222*0.94-H222</f>
+        <f t="shared" si="6"/>
         <v>151.84059999999999</v>
       </c>
       <c r="L222">
-        <f>J222-K222</f>
+        <f t="shared" si="7"/>
         <v>151.84059999999999</v>
       </c>
     </row>
@@ -9303,11 +9324,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J223">
-        <f>G223*0.94-H223</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L223">
-        <f>J223-K223</f>
+        <f t="shared" si="7"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -9340,11 +9361,11 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J224">
-        <f>G224*0.94-H224</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="L224">
-        <f>J224-K224</f>
+        <f t="shared" si="7"/>
         <v>44.38519999999999</v>
       </c>
     </row>
@@ -9377,11 +9398,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J225">
-        <f>G225*0.94-H225</f>
+        <f t="shared" si="6"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L225">
-        <f>J225-K225</f>
+        <f t="shared" si="7"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -9414,11 +9435,11 @@
         <v>160.02099999999999</v>
       </c>
       <c r="J226">
-        <f>G226*0.94-H226</f>
+        <f t="shared" si="6"/>
         <v>148.01944</v>
       </c>
       <c r="L226">
-        <f>J226-K226</f>
+        <f t="shared" si="7"/>
         <v>148.01944</v>
       </c>
     </row>
@@ -9451,11 +9472,11 @@
         <v>35.287999999999997</v>
       </c>
       <c r="J227">
-        <f>G227*0.94-H227</f>
+        <f t="shared" si="6"/>
         <v>32.641400000000004</v>
       </c>
       <c r="L227">
-        <f>J227-K227</f>
+        <f t="shared" si="7"/>
         <v>32.641400000000004</v>
       </c>
     </row>
@@ -9488,11 +9509,11 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J228">
-        <f>G228*0.94-H228</f>
+        <f t="shared" si="6"/>
         <v>28.297599999999999</v>
       </c>
       <c r="L228">
-        <f>J228-K228</f>
+        <f t="shared" si="7"/>
         <v>28.297599999999999</v>
       </c>
     </row>
@@ -9525,11 +9546,11 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J229">
-        <f>G229*0.94-H229</f>
+        <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
       <c r="L229">
-        <f>J229-K229</f>
+        <f t="shared" si="7"/>
         <v>22.1038</v>
       </c>
     </row>
@@ -9562,11 +9583,11 @@
         <v>47.8</v>
       </c>
       <c r="J230">
-        <f>G230*0.94-H230</f>
+        <f t="shared" si="6"/>
         <v>44.215000000000003</v>
       </c>
       <c r="L230">
-        <f>J230-K230</f>
+        <f t="shared" si="7"/>
         <v>44.215000000000003</v>
       </c>
     </row>
@@ -9599,11 +9620,11 @@
         <v>34.76</v>
       </c>
       <c r="J231">
-        <f>G231*0.94-H231</f>
+        <f t="shared" si="6"/>
         <v>32.153000000000006</v>
       </c>
       <c r="L231">
-        <f>J231-K231</f>
+        <f t="shared" si="7"/>
         <v>32.153000000000006</v>
       </c>
     </row>
@@ -9636,11 +9657,11 @@
         <v>38.423999999999999</v>
       </c>
       <c r="J232">
-        <f>G232*0.94-H232</f>
+        <f t="shared" si="6"/>
         <v>35.542199999999994</v>
       </c>
       <c r="L232">
-        <f>J232-K232</f>
+        <f t="shared" si="7"/>
         <v>35.542199999999994</v>
       </c>
     </row>
@@ -9673,11 +9694,11 @@
         <v>46.335999999999999</v>
       </c>
       <c r="J233">
-        <f>G233*0.94-H233</f>
+        <f t="shared" si="6"/>
         <v>42.860799999999998</v>
       </c>
       <c r="L233">
-        <f>J233-K233</f>
+        <f t="shared" si="7"/>
         <v>42.860799999999998</v>
       </c>
     </row>
@@ -9710,11 +9731,11 @@
         <v>46.927999999999997</v>
       </c>
       <c r="J234">
-        <f>G234*0.94-H234</f>
+        <f t="shared" si="6"/>
         <v>43.408399999999993</v>
       </c>
       <c r="L234">
-        <f>J234-K234</f>
+        <f t="shared" si="7"/>
         <v>43.408399999999993</v>
       </c>
     </row>
@@ -9747,11 +9768,11 @@
         <v>40.024000000000001</v>
       </c>
       <c r="J235">
-        <f>G235*0.94-H235</f>
+        <f t="shared" si="6"/>
         <v>37.022199999999998</v>
       </c>
       <c r="L235">
-        <f>J235-K235</f>
+        <f t="shared" si="7"/>
         <v>37.022199999999998</v>
       </c>
     </row>
@@ -9784,11 +9805,11 @@
         <v>20.143999999999998</v>
       </c>
       <c r="J236">
-        <f>G236*0.94-H236</f>
+        <f t="shared" si="6"/>
         <v>18.633200000000002</v>
       </c>
       <c r="L236">
-        <f>J236-K236</f>
+        <f t="shared" si="7"/>
         <v>18.633200000000002</v>
       </c>
     </row>
@@ -9821,11 +9842,11 @@
         <v>9.68</v>
       </c>
       <c r="J237">
-        <f>G237*0.94-H237</f>
+        <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="L237">
-        <f>J237-K237</f>
+        <f t="shared" si="7"/>
         <v>8.9539999999999988</v>
       </c>
     </row>
@@ -9858,11 +9879,11 @@
         <v>90.097999999999999</v>
       </c>
       <c r="J238">
-        <f>G238*0.94-H238</f>
+        <f t="shared" si="6"/>
         <v>83.340679999999992</v>
       </c>
       <c r="L238">
-        <f>J238-K238</f>
+        <f t="shared" si="7"/>
         <v>83.340679999999992</v>
       </c>
     </row>
@@ -9895,11 +9916,11 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J239">
-        <f>G239*0.94-H239</f>
+        <f t="shared" si="6"/>
         <v>33.4998</v>
       </c>
       <c r="L239">
-        <f>J239-K239</f>
+        <f t="shared" si="7"/>
         <v>33.4998</v>
       </c>
     </row>
@@ -9932,11 +9953,11 @@
         <v>115.458</v>
       </c>
       <c r="J240">
-        <f>G240*0.94-H240</f>
+        <f t="shared" si="6"/>
         <v>106.79867999999999</v>
       </c>
       <c r="L240">
-        <f>J240-K240</f>
+        <f t="shared" si="7"/>
         <v>106.79867999999999</v>
       </c>
     </row>
@@ -9969,11 +9990,11 @@
         <v>70.248000000000005</v>
       </c>
       <c r="J241">
-        <f>G241*0.94-H241</f>
+        <f t="shared" si="6"/>
         <v>64.979399999999998</v>
       </c>
       <c r="L241">
-        <f>J241-K241</f>
+        <f t="shared" si="7"/>
         <v>64.979399999999998</v>
       </c>
     </row>
@@ -10006,11 +10027,11 @@
         <v>164.15199999999999</v>
       </c>
       <c r="J242">
-        <f>G242*0.94-H242</f>
+        <f t="shared" si="6"/>
         <v>151.84059999999999</v>
       </c>
       <c r="L242">
-        <f>J242-K242</f>
+        <f t="shared" si="7"/>
         <v>151.84059999999999</v>
       </c>
     </row>
@@ -10043,11 +10064,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J243">
-        <f>G243*0.94-H243</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L243">
-        <f>J243-K243</f>
+        <f t="shared" si="7"/>
         <v>39.094199999999994</v>
       </c>
     </row>
@@ -10080,11 +10101,11 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J244">
-        <f>G244*0.94-H244</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="L244">
-        <f>J244-K244</f>
+        <f t="shared" si="7"/>
         <v>44.38519999999999</v>
       </c>
     </row>
@@ -10117,11 +10138,11 @@
         <v>56.503999999999998</v>
       </c>
       <c r="J245">
-        <f>G245*0.94-H245</f>
+        <f t="shared" si="6"/>
         <v>52.266199999999991</v>
       </c>
       <c r="L245">
-        <f>J245-K245</f>
+        <f t="shared" si="7"/>
         <v>52.266199999999991</v>
       </c>
     </row>
@@ -10154,11 +10175,11 @@
         <v>94.512</v>
       </c>
       <c r="J246">
-        <f>G246*0.94-H246</f>
+        <f t="shared" si="6"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L246">
-        <f>J246-K246</f>
+        <f t="shared" si="7"/>
         <v>87.423599999999993</v>
       </c>
     </row>
@@ -10191,11 +10212,11 @@
         <v>43.503999999999998</v>
       </c>
       <c r="J247">
-        <f>G247*0.94-H247</f>
+        <f t="shared" si="6"/>
         <v>40.241199999999999</v>
       </c>
       <c r="L247">
-        <f>J247-K247</f>
+        <f t="shared" si="7"/>
         <v>40.241199999999999</v>
       </c>
     </row>
@@ -10228,11 +10249,11 @@
         <v>45.607999999999997</v>
       </c>
       <c r="J248">
-        <f>G248*0.94-H248</f>
+        <f t="shared" si="6"/>
         <v>42.187399999999997</v>
       </c>
       <c r="L248">
-        <f>J248-K248</f>
+        <f t="shared" si="7"/>
         <v>42.187399999999997</v>
       </c>
     </row>
@@ -10265,11 +10286,11 @@
         <v>43.72</v>
       </c>
       <c r="J249">
-        <f>G249*0.94-H249</f>
+        <f t="shared" si="6"/>
         <v>40.440999999999995</v>
       </c>
       <c r="L249">
-        <f>J249-K249</f>
+        <f t="shared" si="7"/>
         <v>40.440999999999995</v>
       </c>
     </row>
@@ -10302,11 +10323,11 @@
         <v>45.072000000000003</v>
       </c>
       <c r="J250">
-        <f>G250*0.94-H250</f>
+        <f t="shared" si="6"/>
         <v>41.691600000000001</v>
       </c>
       <c r="L250">
-        <f>J250-K250</f>
+        <f t="shared" si="7"/>
         <v>41.691600000000001</v>
       </c>
     </row>
@@ -10339,11 +10360,11 @@
         <v>38.456000000000003</v>
       </c>
       <c r="J251">
-        <f>G251*0.94-H251</f>
+        <f t="shared" si="6"/>
         <v>35.571799999999996</v>
       </c>
       <c r="L251">
-        <f>J251-K251</f>
+        <f t="shared" si="7"/>
         <v>35.571799999999996</v>
       </c>
     </row>
@@ -10376,11 +10397,11 @@
         <v>3.456</v>
       </c>
       <c r="J252">
-        <f>G252*0.94-H252</f>
+        <f t="shared" si="6"/>
         <v>3.1968000000000005</v>
       </c>
       <c r="L252">
-        <f>J252-K252</f>
+        <f t="shared" si="7"/>
         <v>3.1968000000000005</v>
       </c>
     </row>
@@ -10413,11 +10434,11 @@
         <v>65.352000000000004</v>
       </c>
       <c r="J253">
-        <f>G253*0.94-H253</f>
+        <f t="shared" si="6"/>
         <v>60.450599999999987</v>
       </c>
       <c r="L253">
-        <f>J253-K253</f>
+        <f t="shared" si="7"/>
         <v>60.450599999999987</v>
       </c>
     </row>
@@ -10450,11 +10471,11 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J254">
-        <f>G254*0.94-H254</f>
+        <f t="shared" si="6"/>
         <v>28.297599999999999</v>
       </c>
       <c r="L254">
-        <f>J254-K254</f>
+        <f t="shared" si="7"/>
         <v>28.297599999999999</v>
       </c>
     </row>
@@ -10487,11 +10508,11 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J255">
-        <f>G255*0.94-H255</f>
+        <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
       <c r="L255">
-        <f>J255-K255</f>
+        <f t="shared" si="7"/>
         <v>22.1038</v>
       </c>
     </row>
@@ -10524,11 +10545,11 @@
         <v>35.287999999999997</v>
       </c>
       <c r="J256">
-        <f>G256*0.94-H256</f>
+        <f t="shared" si="6"/>
         <v>32.641400000000004</v>
       </c>
       <c r="L256">
-        <f>J256-K256</f>
+        <f t="shared" si="7"/>
         <v>32.641400000000004</v>
       </c>
     </row>
@@ -10561,11 +10582,11 @@
         <v>39.863999999999997</v>
       </c>
       <c r="J257">
-        <f>G257*0.94-H257</f>
+        <f t="shared" si="6"/>
         <v>36.874199999999995</v>
       </c>
       <c r="L257">
-        <f>J257-K257</f>
+        <f t="shared" si="7"/>
         <v>36.874199999999995</v>
       </c>
     </row>
@@ -10598,11 +10619,11 @@
         <v>41.152000000000001</v>
       </c>
       <c r="J258">
-        <f>G258*0.94-H258</f>
+        <f t="shared" ref="J258:J265" si="8">G258*0.94-H258</f>
         <v>38.065599999999989</v>
       </c>
       <c r="L258">
-        <f>J258-K258</f>
+        <f t="shared" ref="L258:L321" si="9">J258-K258</f>
         <v>38.065599999999989</v>
       </c>
     </row>
@@ -10635,11 +10656,11 @@
         <v>52.872</v>
       </c>
       <c r="J259">
-        <f>G259*0.94-H259</f>
+        <f t="shared" si="8"/>
         <v>48.906599999999997</v>
       </c>
       <c r="L259">
-        <f>J259-K259</f>
+        <f t="shared" si="9"/>
         <v>48.906599999999997</v>
       </c>
     </row>
@@ -10672,11 +10693,11 @@
         <v>76.128</v>
       </c>
       <c r="J260">
-        <f>G260*0.94-H260</f>
+        <f t="shared" si="8"/>
         <v>70.418399999999991</v>
       </c>
       <c r="L260">
-        <f>J260-K260</f>
+        <f t="shared" si="9"/>
         <v>70.418399999999991</v>
       </c>
     </row>
@@ -10709,11 +10730,11 @@
         <v>155.48500000000001</v>
       </c>
       <c r="J261">
-        <f>G261*0.94-H261</f>
+        <f t="shared" si="8"/>
         <v>143.82363999999998</v>
       </c>
       <c r="L261">
-        <f>J261-K261</f>
+        <f t="shared" si="9"/>
         <v>143.82363999999998</v>
       </c>
     </row>
@@ -10746,11 +10767,11 @@
         <v>42.64</v>
       </c>
       <c r="J262">
-        <f>G262*0.94-H262</f>
+        <f t="shared" si="8"/>
         <v>39.441999999999993</v>
       </c>
       <c r="L262">
-        <f>J262-K262</f>
+        <f t="shared" si="9"/>
         <v>39.441999999999993</v>
       </c>
     </row>
@@ -10783,11 +10804,11 @@
         <v>47.823999999999998</v>
       </c>
       <c r="J263">
-        <f>G263*0.94-H263</f>
+        <f t="shared" si="8"/>
         <v>44.237200000000001</v>
       </c>
       <c r="L263">
-        <f>J263-K263</f>
+        <f t="shared" si="9"/>
         <v>44.237200000000001</v>
       </c>
     </row>
@@ -10820,11 +10841,11 @@
         <v>46.872</v>
       </c>
       <c r="J264">
-        <f>G264*0.94-H264</f>
+        <f t="shared" si="8"/>
         <v>43.3566</v>
       </c>
       <c r="L264">
-        <f>J264-K264</f>
+        <f t="shared" si="9"/>
         <v>43.3566</v>
       </c>
     </row>
@@ -10857,12 +10878,202 @@
         <v>18.248000000000001</v>
       </c>
       <c r="J265">
-        <f>G265*0.94-H265</f>
+        <f t="shared" si="8"/>
         <v>16.879399999999997</v>
       </c>
       <c r="L265">
-        <f>J265-K265</f>
+        <f t="shared" si="9"/>
         <v>16.879399999999997</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A266" s="5">
+        <v>1</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D266" s="5">
+        <v>801665350</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F266" s="6">
+        <v>46212</v>
+      </c>
+      <c r="G266" s="5">
+        <v>27.78</v>
+      </c>
+      <c r="H266" s="5">
+        <v>5.556</v>
+      </c>
+      <c r="I266" s="5">
+        <v>22.224</v>
+      </c>
+      <c r="J266" s="4">
+        <f t="shared" ref="J266:J270" si="10">G266*0.94-H266</f>
+        <v>20.557199999999998</v>
+      </c>
+      <c r="K266" s="4"/>
+      <c r="L266" s="4">
+        <f t="shared" ref="L266:L270" si="11">J266-K266</f>
+        <v>20.557199999999998</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A267" s="5">
+        <v>2</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D267" s="5">
+        <v>801667051</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F267" s="6">
+        <v>46227</v>
+      </c>
+      <c r="G267" s="5">
+        <v>25.1</v>
+      </c>
+      <c r="H267" s="5">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="I267" s="5">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="J267" s="4">
+        <f t="shared" si="10"/>
+        <v>18.574000000000002</v>
+      </c>
+      <c r="K267" s="4"/>
+      <c r="L267" s="4">
+        <f t="shared" si="11"/>
+        <v>18.574000000000002</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A268" s="5">
+        <v>3</v>
+      </c>
+      <c r="B268" s="5">
+        <v>35716</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D268" s="5">
+        <v>801667315</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F268" s="6">
+        <v>46230</v>
+      </c>
+      <c r="G268" s="5">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="H268" s="5">
+        <v>0</v>
+      </c>
+      <c r="I268" s="5">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="J268" s="4">
+        <f t="shared" si="10"/>
+        <v>16.506399999999999</v>
+      </c>
+      <c r="K268" s="4"/>
+      <c r="L268" s="4">
+        <f t="shared" si="11"/>
+        <v>16.506399999999999</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
+        <v>4</v>
+      </c>
+      <c r="B269" s="5">
+        <v>19077</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D269" s="5">
+        <v>801667317</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F269" s="6">
+        <v>46230</v>
+      </c>
+      <c r="G269" s="5">
+        <v>37.18</v>
+      </c>
+      <c r="H269" s="5">
+        <v>0</v>
+      </c>
+      <c r="I269" s="5">
+        <v>37.18</v>
+      </c>
+      <c r="J269" s="4">
+        <f t="shared" si="10"/>
+        <v>34.949199999999998</v>
+      </c>
+      <c r="K269" s="4"/>
+      <c r="L269" s="4">
+        <f t="shared" si="11"/>
+        <v>34.949199999999998</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
+        <v>5</v>
+      </c>
+      <c r="B270" s="5">
+        <v>19076</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D270" s="5">
+        <v>801667313</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F270" s="6">
+        <v>46230</v>
+      </c>
+      <c r="G270" s="5">
+        <v>30.35</v>
+      </c>
+      <c r="H270" s="5">
+        <v>0</v>
+      </c>
+      <c r="I270" s="5">
+        <v>30.35</v>
+      </c>
+      <c r="J270" s="4">
+        <f t="shared" si="10"/>
+        <v>28.529</v>
+      </c>
+      <c r="K270" s="4"/>
+      <c r="L270" s="4">
+        <f t="shared" si="11"/>
+        <v>28.529</v>
       </c>
     </row>
   </sheetData>
